--- a/manual-testing/Jumia-Login-TestCases.xlsx
+++ b/manual-testing/Jumia-Login-TestCases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/870b8592959c4359/Desktop/claude tasks/QA-portfolio/manual-testing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{41EB0DF5-221F-4400-9090-E9406EB398D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B07D2C6-10C7-4D0D-9415-0E04CBF6AEB3}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{41EB0DF5-221F-4400-9090-E9406EB398D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{002237F4-EECF-4635-A985-664256D2241E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="80">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -245,6 +245,27 @@
   </si>
   <si>
     <t>The user has been registered</t>
+  </si>
+  <si>
+    <t>TC-Filter&amp;Sort-001</t>
+  </si>
+  <si>
+    <t>TC-Filter&amp;Sort-002</t>
+  </si>
+  <si>
+    <t>TC-Filter&amp;Sort-003</t>
+  </si>
+  <si>
+    <t>TC-Filter&amp;Sort-004</t>
+  </si>
+  <si>
+    <t>TC-Filter&amp;Sort-005</t>
+  </si>
+  <si>
+    <t>TC-Filter&amp;Sort-006</t>
+  </si>
+  <si>
+    <t>Filter&amp;Sort</t>
   </si>
 </sst>
 </file>
@@ -1217,7 +1238,7 @@
   <dimension ref="A1:T31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.28515625" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -1948,9 +1969,13 @@
       <c r="P23" s="10"/>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" s="9"/>
+      <c r="A24" s="9" t="s">
+        <v>73</v>
+      </c>
       <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
+      <c r="C24" s="10" t="s">
+        <v>79</v>
+      </c>
       <c r="D24" s="10"/>
       <c r="E24" s="10"/>
       <c r="F24" s="10"/>
@@ -1966,9 +1991,13 @@
       <c r="P24" s="10"/>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" s="15"/>
+      <c r="A25" s="9" t="s">
+        <v>74</v>
+      </c>
       <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
+      <c r="C25" s="10" t="s">
+        <v>79</v>
+      </c>
       <c r="D25" s="10"/>
       <c r="E25" s="10"/>
       <c r="F25" s="10"/>
@@ -1984,9 +2013,13 @@
       <c r="P25" s="10"/>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" s="15"/>
+      <c r="A26" s="9" t="s">
+        <v>75</v>
+      </c>
       <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
+      <c r="C26" s="10" t="s">
+        <v>79</v>
+      </c>
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
@@ -2002,9 +2035,13 @@
       <c r="P26" s="10"/>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27" s="15"/>
+      <c r="A27" s="9" t="s">
+        <v>76</v>
+      </c>
       <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
+      <c r="C27" s="10" t="s">
+        <v>79</v>
+      </c>
       <c r="D27" s="10"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
@@ -2020,9 +2057,13 @@
       <c r="P27" s="10"/>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" s="15"/>
+      <c r="A28" s="9" t="s">
+        <v>77</v>
+      </c>
       <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
+      <c r="C28" s="10" t="s">
+        <v>79</v>
+      </c>
       <c r="D28" s="10"/>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
@@ -2038,9 +2079,13 @@
       <c r="P28" s="10"/>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A29" s="15"/>
+      <c r="A29" s="9" t="s">
+        <v>78</v>
+      </c>
       <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
+      <c r="C29" s="10" t="s">
+        <v>79</v>
+      </c>
       <c r="D29" s="10"/>
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
